--- a/artfynd/A 17606-2026 artfynd.xlsx
+++ b/artfynd/A 17606-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>94444787</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,15 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94523113</v>
+        <v>94523111</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462549.8422065094</v>
+        <v>462680</v>
       </c>
       <c r="R3" t="n">
-        <v>7104673.590610865</v>
+        <v>7104586</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +867,9 @@
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -916,15 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94523111</v>
+        <v>94523113</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -960,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462679.8678831077</v>
+        <v>462550</v>
       </c>
       <c r="R4" t="n">
-        <v>7104586.214458161</v>
+        <v>7104674</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,19 +973,9 @@
           <t>2021-06-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-06-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1034,6 +1004,101 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>94492697</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Krokom, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>462258</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7104286</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17606-2026 artfynd.xlsx
+++ b/artfynd/A 17606-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94444787</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94523111</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94523113</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,8 +1119,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94492697</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>